--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104760_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104760_W34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8095</v>
+        <v>4.8549</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1188</v>
+        <v>2.2897</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6907</v>
+        <v>2.5652</v>
       </c>
       <c r="G2" t="n">
         <v>2.3675</v>
@@ -610,13 +610,13 @@
         <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6307</v>
+        <v>0.6761</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1099</v>
+        <v>0.2808</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5208</v>
+        <v>0.3953</v>
       </c>
       <c r="V2" t="n">
         <v>0.2179</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4976</v>
+        <v>4.205</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9582</v>
+        <v>2.6029</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5394</v>
+        <v>1.6021</v>
       </c>
       <c r="G3" t="n">
         <v>2.774</v>
@@ -688,13 +688,13 @@
         <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.288</v>
+        <v>-0.0046</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3714</v>
+        <v>0.0161</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0834</v>
+        <v>-0.0207</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1578</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.197</v>
+        <v>1.8276</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9399</v>
+        <v>3.4137</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7429</v>
+        <v>-1.5861</v>
       </c>
       <c r="G4" t="n">
         <v>0.1548</v>
@@ -766,13 +766,13 @@
         <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.1612</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6785</v>
+        <v>-0.2047</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1133</v>
+        <v>0.0435</v>
       </c>
       <c r="V4" t="n">
         <v>1.3788</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0971</v>
+        <v>1.2469</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3104</v>
+        <v>0.4288</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7867</v>
+        <v>0.8181</v>
       </c>
       <c r="G5" t="n">
         <v>1.2156</v>
@@ -844,13 +844,13 @@
         <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3368</v>
+        <v>0.4866</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0926</v>
+        <v>0.2111</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2442</v>
+        <v>0.2755</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3487</v>
+        <v>1.1745</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9481000000000001</v>
+        <v>1.3034</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5995</v>
+        <v>-0.129</v>
       </c>
       <c r="G6" t="n">
         <v>3.717</v>
@@ -922,13 +922,13 @@
         <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4889</v>
+        <v>-0.663</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.697</v>
+        <v>-0.3417</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="V6" t="n">
         <v>1.3074</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1072</v>
+        <v>0.1175</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1341</v>
+        <v>0.2212</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2414</v>
+        <v>-0.1037</v>
       </c>
       <c r="G7" t="n">
         <v>2.2612</v>
@@ -1000,13 +1000,13 @@
         <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.797</v>
+        <v>0.8073</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3071</v>
+        <v>0.0483</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1041</v>
+        <v>0.7591</v>
       </c>
       <c r="V7" t="n">
         <v>0.6912</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0217</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1266</v>
+        <v>0.0325</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3523</v>
@@ -1078,13 +1078,13 @@
         <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1464</v>
+        <v>0.0523</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1394</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2858</v>
+        <v>0.1917</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4689</v>
+        <v>-3.9161</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5169</v>
+        <v>-0.2674</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9519</v>
+        <v>-3.6487</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1344</v>
+        <v>-0.2356</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-1.2872</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5432</v>
+        <v>1.0516</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4834</v>
+        <v>0.1349</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3717</v>
+        <v>-0.669</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1117</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6179</v>
+        <v>-0.3704</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9629</v>
+        <v>-0.6182</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6549</v>
+        <v>0.2477</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.0974</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.5526</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7629</v>
+        <v>-0.3227</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4628</v>
+        <v>-0.5601</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3001</v>
+        <v>0.2374</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-3.8132</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0895</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0895</v>
+        <v>-3.9709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9091</v>
+        <v>-4.3808</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3859</v>
+        <v>-2.7641</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5233</v>
+        <v>-1.6167</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2356</v>
+        <v>-3.7327</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2872</v>
+        <v>0.0256</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0516</v>
+        <v>-3.7583</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1349</v>
+        <v>-2.3886</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.669</v>
+        <v>0.6583</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8038999999999999</v>
+        <v>-3.0469</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3704</v>
+        <v>-1.3441</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6182</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2477</v>
+        <v>-0.7114</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4553</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4553</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3157</v>
+        <v>0.4005</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6785</v>
+        <v>0.2666</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3628</v>
+        <v>0.1339</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.8132</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1578</v>
+        <v>1.6342</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.9709</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3705</v>
+        <v>-4.636</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4087</v>
+        <v>-2.4645</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9618</v>
+        <v>-2.1715</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7327</v>
+        <v>-1.1344</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0256</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7583</v>
+        <v>-0.5432</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3886</v>
+        <v>0.4834</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6583</v>
+        <v>0.3717</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.0469</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3441</v>
+        <v>-1.6179</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.9629</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7114</v>
+        <v>-0.6549</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5934</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2763</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6829</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4109</v>
+        <v>0.5958</v>
       </c>
       <c r="T12" t="n">
-        <v>0.622</v>
+        <v>0.5152</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2111</v>
+        <v>0.0805</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5447</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6342</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>-1.0895</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2435</v>
+        <v>-6.3343</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.5067</v>
+        <v>-7.4407</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2632</v>
+        <v>1.1064</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8485</v>
@@ -1468,13 +1468,13 @@
         <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3366</v>
+        <v>0.5726</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8364</v>
+        <v>0.2296</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4999</v>
+        <v>0.343</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3268</v>
@@ -1504,19 +1504,19 @@
         <v>-6.0856</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.781799999999999</v>
+        <v>-2.7819</v>
       </c>
       <c r="F14" t="n">
         <v>-3.3038</v>
       </c>
       <c r="G14" t="n">
-        <v>3.014200000000002</v>
+        <v>3.014200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8036</v>
+        <v>3.803600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7895000000000003</v>
+        <v>-0.7894999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>9.658899999999999</v>
@@ -1549,10 +1549,10 @@
         <v>2.4397</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3218000000000001</v>
+        <v>0.3218</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1181</v>
+        <v>2.1179</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1578000000000002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9961</v>
+        <v>5.7793</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1918</v>
+        <v>3.8445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8043</v>
+        <v>1.9348</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8391999999999999</v>
+        <v>1.2524</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9217</v>
+        <v>-0.806</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0825</v>
+        <v>2.0583</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5804</v>
+        <v>2.1239</v>
       </c>
       <c r="K15" t="n">
-        <v>2.899</v>
+        <v>0.5161</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3186</v>
+        <v>1.6077</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7412</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9774</v>
+        <v>-1.3221</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2361</v>
+        <v>0.4506</v>
       </c>
       <c r="P15" t="n">
-        <v>4.0974</v>
+        <v>2.7316</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>4.0974</v>
+        <v>3.8697</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3274</v>
+        <v>-0.5413</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.5674</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3979</v>
+        <v>0.0261</v>
       </c>
       <c r="V15" t="n">
-        <v>0.387</v>
+        <v>2.3367</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3367</v>
+        <v>3.4262</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.9497</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7366</v>
+        <v>5.1016</v>
       </c>
       <c r="E16" t="n">
-        <v>2.897</v>
+        <v>3.5472</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8396</v>
+        <v>1.5545</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2524</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.806</v>
+        <v>1.9217</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0583</v>
+        <v>-1.0825</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1239</v>
+        <v>1.5804</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5161</v>
+        <v>2.899</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6077</v>
+        <v>-1.3186</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8715000000000001</v>
+        <v>-0.7412</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3221</v>
+        <v>-0.9774</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4506</v>
+        <v>0.2361</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7316</v>
+        <v>4.0974</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.8697</v>
+        <v>4.0974</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5841</v>
+        <v>-0.2219</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5149</v>
+        <v>-0.37</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1481</v>
       </c>
       <c r="V16" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="W16" t="n">
         <v>2.3367</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.4262</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.0895</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7197</v>
+        <v>3.5212</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5833</v>
+        <v>2.6357</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1364</v>
+        <v>0.8854</v>
       </c>
       <c r="G17" t="n">
         <v>2.383</v>
@@ -1780,13 +1780,13 @@
         <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>2.109</v>
+        <v>0.9105</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3887</v>
+        <v>0.4411</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.4694</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0334</v>
+        <v>1.8695</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7963</v>
+        <v>-1.0857</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8297</v>
+        <v>2.9552</v>
       </c>
       <c r="G18" t="n">
         <v>1.2855</v>
@@ -1858,13 +1858,13 @@
         <v>2.7316</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4586</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1664</v>
+        <v>-0.4558</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2922</v>
+        <v>-0.1667</v>
       </c>
       <c r="V18" t="n">
         <v>-0.387</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.849</v>
+        <v>-0.2602</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9489</v>
+        <v>0.2698</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7413</v>
+        <v>-2.3931</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0165</v>
+        <v>0.0862</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7578</v>
+        <v>-2.4793</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7721</v>
+        <v>-0.3725</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4479</v>
+        <v>1.1926</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.22</v>
+        <v>-1.5651</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0308</v>
+        <v>-2.0207</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4314</v>
+        <v>-1.1064</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4622</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4553</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5934</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7014</v>
+        <v>-0.2998</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0283</v>
+        <v>-0.5415</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7297</v>
+        <v>0.2418</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3155</v>
+        <v>1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0895</v>
+        <v>1.792</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0815</v>
+        <v>-0.0186</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.9675</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0136</v>
+        <v>0.9489</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3931</v>
+        <v>-0.7413</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0862</v>
+        <v>1.0165</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4793</v>
+        <v>-1.7578</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3725</v>
+        <v>-0.7721</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1926</v>
+        <v>1.4479</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5651</v>
+        <v>-2.22</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0207</v>
+        <v>0.0308</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1064</v>
+        <v>-0.4314</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9143</v>
+        <v>0.4622</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9105</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0487</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2278</v>
+        <v>0.583</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1862</v>
+        <v>-0.1467</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0416</v>
+        <v>0.7297</v>
       </c>
       <c r="V20" t="n">
-        <v>1.792</v>
+        <v>-0.3155</v>
       </c>
       <c r="W20" t="n">
-        <v>1.792</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5173</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7442</v>
+        <v>-1.9811</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2269</v>
+        <v>1.4151</v>
       </c>
       <c r="G21" t="n">
         <v>1.481</v>
@@ -2092,13 +2092,13 @@
         <v>2.7316</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5901</v>
+        <v>-0.6388</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1165</v>
+        <v>-0.3534</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4736</v>
+        <v>-0.2854</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8634</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5584</v>
+        <v>-0.9376</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9932</v>
+        <v>0.7402</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5515</v>
+        <v>-1.6778</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4756</v>
+        <v>-1.2246</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2459</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7704</v>
+        <v>-0.7191</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0285</v>
+        <v>0.954</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1828</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1543</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4471</v>
+        <v>-2.1786</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0631</v>
+        <v>-1.4223</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.384</v>
+        <v>-0.7563</v>
       </c>
       <c r="P22" t="n">
-        <v>2.0487</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0487</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.042</v>
+        <v>-0.1895</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0217</v>
+        <v>-0.1165</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0637</v>
+        <v>-0.073</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0895</v>
+        <v>0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0895</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1269</v>
+        <v>-0.9694</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7402</v>
+        <v>0.5194</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8671</v>
+        <v>-1.4888</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2246</v>
+        <v>-1.4756</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-2.2459</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7191</v>
+        <v>0.7704</v>
       </c>
       <c r="J23" t="n">
-        <v>0.954</v>
+        <v>-0.0285</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9167999999999999</v>
+        <v>-1.1828</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0372</v>
+        <v>1.1543</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1786</v>
+        <v>-1.4471</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4223</v>
+        <v>-1.0631</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7563</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4553</v>
+        <v>2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8211</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3788</v>
+        <v>-0.4531</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1165</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2623</v>
+        <v>-1.0009</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9317</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1789</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2472</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8509</v>
+        <v>-1.4734</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1169</v>
+        <v>0.2726</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.734</v>
+        <v>-1.7459</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8195</v>
+        <v>-1.8447</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9913</v>
+        <v>-2.361</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8282</v>
+        <v>0.5163</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.629</v>
+        <v>-0.1964</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0862</v>
+        <v>-1.0967</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.9002</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1906</v>
+        <v>-1.6483</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0775</v>
+        <v>-1.2643</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.113</v>
+        <v>-0.384</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6829</v>
+        <v>1.8211</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6829</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1695</v>
+        <v>-0.3602</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4879</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3184</v>
+        <v>0.2603</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5447</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5447</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2376</v>
+        <v>-1.7081</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0828</v>
+        <v>-0.88</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1548</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.8447</v>
+        <v>-1.8195</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.361</v>
+        <v>-0.9913</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5163</v>
+        <v>-0.8282</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1964</v>
+        <v>-0.629</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.0967</v>
+        <v>0.0862</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9002</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6483</v>
+        <v>-1.1906</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.2643</v>
+        <v>-1.0775</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.384</v>
+        <v>-0.113</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8211</v>
+        <v>0.6829</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8211</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1244</v>
+        <v>-0.0267</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9758</v>
+        <v>-0.251</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1486</v>
+        <v>0.2243</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0895</v>
+        <v>-0.5447</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1789</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2906</v>
+        <v>-3.733</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6076</v>
+        <v>-3.0814</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.6516</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7564</v>
@@ -2482,13 +2482,13 @@
         <v>0.2276</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6526</v>
+        <v>0.2102</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7896</v>
+        <v>0.3159</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.085500000000001</v>
+        <v>6.8751</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3039</v>
+        <v>3.303700000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.7818</v>
+        <v>3.5715</v>
       </c>
       <c r="G27" t="n">
         <v>-3.0141</v>
@@ -2530,16 +2530,16 @@
         <v>-3.8038</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7896999999999998</v>
+        <v>0.7897000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>6.644599999999999</v>
+        <v>6.6446</v>
       </c>
       <c r="K27" t="n">
-        <v>6.4705</v>
+        <v>6.470499999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1738999999999998</v>
+        <v>0.1739000000000002</v>
       </c>
       <c r="M27" t="n">
         <v>-9.658900000000001</v>
@@ -2560,16 +2560,16 @@
         <v>23.9014</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.4397</v>
+        <v>-1.6501</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.1178</v>
+        <v>-2.1179</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3218</v>
+        <v>0.4679999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1578000000000006</v>
+        <v>0.1578000000000002</v>
       </c>
       <c r="W27" t="n">
         <v>11.2967</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104760_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104760_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.9791</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0293</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-3.9709</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.2965</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104760_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-11.1387</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
